--- a/artfynd/A 58480-2025 artfynd.xlsx
+++ b/artfynd/A 58480-2025 artfynd.xlsx
@@ -1014,6 +1014,16 @@
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Lars Karlsson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Lars Karlsson</t>
+        </is>
+      </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
@@ -1115,6 +1125,16 @@
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Lars Karlsson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Lars Karlsson</t>
+        </is>
+      </c>
       <c r="AY5" t="inlineStr"/>
     </row>
   </sheetData>

--- a/artfynd/A 58480-2025 artfynd.xlsx
+++ b/artfynd/A 58480-2025 artfynd.xlsx
@@ -920,7 +920,7 @@
         <v>129821832</v>
       </c>
       <c r="B4" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1031,7 +1031,7 @@
         <v>129821830</v>
       </c>
       <c r="B5" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 58480-2025 artfynd.xlsx
+++ b/artfynd/A 58480-2025 artfynd.xlsx
@@ -920,7 +920,7 @@
         <v>129821832</v>
       </c>
       <c r="B4" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1031,7 +1031,7 @@
         <v>129821830</v>
       </c>
       <c r="B5" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 58480-2025 artfynd.xlsx
+++ b/artfynd/A 58480-2025 artfynd.xlsx
@@ -920,7 +920,7 @@
         <v>129821832</v>
       </c>
       <c r="B4" t="n">
-        <v>98780</v>
+        <v>98790</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1031,7 +1031,7 @@
         <v>129821830</v>
       </c>
       <c r="B5" t="n">
-        <v>98780</v>
+        <v>98790</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 58480-2025 artfynd.xlsx
+++ b/artfynd/A 58480-2025 artfynd.xlsx
@@ -920,7 +920,7 @@
         <v>129821832</v>
       </c>
       <c r="B4" t="n">
-        <v>98790</v>
+        <v>98794</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1031,7 +1031,7 @@
         <v>129821830</v>
       </c>
       <c r="B5" t="n">
-        <v>98790</v>
+        <v>98794</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 58480-2025 artfynd.xlsx
+++ b/artfynd/A 58480-2025 artfynd.xlsx
@@ -920,7 +920,7 @@
         <v>129821832</v>
       </c>
       <c r="B4" t="n">
-        <v>98794</v>
+        <v>98797</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1031,7 +1031,7 @@
         <v>129821830</v>
       </c>
       <c r="B5" t="n">
-        <v>98794</v>
+        <v>98797</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 58480-2025 artfynd.xlsx
+++ b/artfynd/A 58480-2025 artfynd.xlsx
@@ -920,7 +920,7 @@
         <v>129821832</v>
       </c>
       <c r="B4" t="n">
-        <v>98797</v>
+        <v>98798</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1031,7 +1031,7 @@
         <v>129821830</v>
       </c>
       <c r="B5" t="n">
-        <v>98797</v>
+        <v>98798</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 58480-2025 artfynd.xlsx
+++ b/artfynd/A 58480-2025 artfynd.xlsx
@@ -920,7 +920,7 @@
         <v>129821832</v>
       </c>
       <c r="B4" t="n">
-        <v>98798</v>
+        <v>98815</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1031,7 +1031,7 @@
         <v>129821830</v>
       </c>
       <c r="B5" t="n">
-        <v>98798</v>
+        <v>98815</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 58480-2025 artfynd.xlsx
+++ b/artfynd/A 58480-2025 artfynd.xlsx
@@ -920,7 +920,7 @@
         <v>129821832</v>
       </c>
       <c r="B4" t="n">
-        <v>98831</v>
+        <v>98833</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1031,7 +1031,7 @@
         <v>129821830</v>
       </c>
       <c r="B5" t="n">
-        <v>98831</v>
+        <v>98833</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 58480-2025 artfynd.xlsx
+++ b/artfynd/A 58480-2025 artfynd.xlsx
@@ -920,7 +920,7 @@
         <v>129821832</v>
       </c>
       <c r="B4" t="n">
-        <v>98833</v>
+        <v>98920</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1031,7 +1031,7 @@
         <v>129821830</v>
       </c>
       <c r="B5" t="n">
-        <v>98833</v>
+        <v>98920</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 58480-2025 artfynd.xlsx
+++ b/artfynd/A 58480-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>56091946</v>
       </c>
       <c r="B2" t="n">
-        <v>104490</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>107609</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -724,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>631727.0897124066</v>
+        <v>631727</v>
       </c>
       <c r="R2" t="n">
-        <v>6711747.177897189</v>
+        <v>6711747</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -757,19 +752,9 @@
           <t>2015-05-03</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2015-05-03</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -796,15 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>93375812</v>
+        <v>67979918</v>
       </c>
       <c r="B3" t="n">
-        <v>101680</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>107609</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -812,16 +792,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222412</v>
+        <v>219686</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Vätteros</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Lathraea squamaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -831,26 +811,27 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Ambricka båtstad, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>631813.3913704559</v>
+        <v>631701</v>
       </c>
       <c r="R3" t="n">
-        <v>6711965.675501299</v>
+        <v>6711816</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -874,22 +855,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2021-05-13</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2017-05-10</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2021-05-13</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2017-05-10</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -898,56 +869,55 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Astrid Eklund</t>
+          <t>Tommy Löfgren</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Astrid Eklund, Alexandra Astafourova, Ellen Bergenfeldt</t>
+          <t>Tommy Löfgren</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129821832</v>
+        <v>67979920</v>
       </c>
       <c r="B4" t="n">
-        <v>98833</v>
+        <v>107609</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>219686</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vätteros</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lathraea squamaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>45</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -957,17 +927,17 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Ambricka, Upl</t>
+          <t>Ambricka båtstad, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>631847</v>
+        <v>631686</v>
       </c>
       <c r="R4" t="n">
-        <v>6711792</v>
+        <v>6711833</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -991,12 +961,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2017-05-10</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2017-05-10</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1007,21 +977,16 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>Äldre gallrad tallskog</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Lars Karlsson</t>
+          <t>Tommy Löfgren</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Lars Karlsson</t>
+          <t>Tommy Löfgren</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -1031,7 +996,7 @@
         <v>129821830</v>
       </c>
       <c r="B5" t="n">
-        <v>98833</v>
+        <v>99118</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1136,6 +1101,539 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>129821832</v>
+      </c>
+      <c r="B6" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Ambricka, Upl</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>631847</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6711792</v>
+      </c>
+      <c r="S6" t="n">
+        <v>25</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-11-18</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-11-18</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>Äldre gallrad tallskog</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Lars Karlsson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Lars Karlsson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>129821833</v>
+      </c>
+      <c r="B7" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Ambricka, Upl</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>631915</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6711881</v>
+      </c>
+      <c r="S7" t="n">
+        <v>25</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-11-18</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-11-18</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>Äldre blåbärstallskog</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Lars Karlsson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Lars Karlsson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>93157412</v>
+      </c>
+      <c r="B8" t="n">
+        <v>104628</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>222412</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Älvkarleby, Upl</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>631741</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6711972</v>
+      </c>
+      <c r="S8" t="n">
+        <v>25</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2021-05-04</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2021-05-04</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Eva Brandt</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Eva Brandt</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>93375812</v>
+      </c>
+      <c r="B9" t="n">
+        <v>104628</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>222412</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Ambricka båtstad, Upl</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>631813</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6711966</v>
+      </c>
+      <c r="S9" t="n">
+        <v>25</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2021-05-13</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2021-05-13</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Astrid Eklund</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Astrid Eklund, Alexandra Astafourova, Ellen Bergenfeldt</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>67979986</v>
+      </c>
+      <c r="B10" t="n">
+        <v>101228</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Ambricka båtstad, Upl</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>631725</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6711948</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2017-05-26</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2017-05-26</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>eftersökt ej funnen, trots lämplig livsmiljö</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Tommy Löfgren</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Tommy Löfgren</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 58480-2025 artfynd.xlsx
+++ b/artfynd/A 58480-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AZ10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -778,6 +783,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56091946</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -884,6 +894,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67979918</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -990,6 +1005,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67979920</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1101,6 +1121,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129821830</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1212,6 +1237,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129821832</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1323,6 +1353,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129821833</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1426,6 +1461,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/93157412</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1532,6 +1572,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/93375812</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1634,8 +1679,24 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67979986</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>